--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Ra79c3c5900e64310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rbfabb52294b94d54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R058aeac496ef480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Ra981e6f89b274c50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R4db5caf1f9cd406c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rcd72ad52924d4d44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R49498caab41246cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R477808dff3db4421"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R4cd0edde9f574c61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rf7c7bed384b74d26"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -725,7 +725,7 @@
     </x:row>
     <x:row r="9" ht="78" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>reference_members</x:v>
+        <x:v>delivery_paths</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
         <x:v>src/parse_bounces.mjs,reports/parsed_bounces.csv,reports/suppression_updates.csv,reports/retry_plan.csv,reports/bounce_exceptions.csv,reports/domain_summary.csv</x:v>
@@ -734,7 +734,7 @@
         <x:v>相对路径逐字匹配</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>reference.zip成员</x:v>
+        <x:v>Prompt声明的业务交付路径</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
